--- a/companies/dev-mini/Finance/FY2019 Financial Summary.xlsx
+++ b/companies/dev-mini/Finance/FY2019 Financial Summary.xlsx
@@ -507,7 +507,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="3">
-        <v>411100</v>
+        <v>421600</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -515,7 +515,7 @@
         <v>11</v>
       </c>
       <c r="F8" s="3">
-        <v>92800</v>
+        <v>95200</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="3">
-        <v>57650</v>
+        <v>59130</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -531,7 +531,7 @@
         <v>13</v>
       </c>
       <c r="F10" s="3">
-        <v>54340</v>
+        <v>55730</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -539,7 +539,7 @@
         <v>14</v>
       </c>
       <c r="F11" s="3">
-        <v>57840</v>
+        <v>59330</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -548,7 +548,7 @@
       </c>
       <c r="F12" s="4">
         <f>SUM(F7:F11)</f>
-        <v>673730</v>
+        <v>690990</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -557,7 +557,7 @@
       </c>
       <c r="F14" s="4">
         <f>F4-F12</f>
-        <v>176270</v>
+        <v>159010</v>
       </c>
     </row>
   </sheetData>
